--- a/mr-dashboards/mr2025/resources/MetadataFailingValidationAllEndpoints.xlsx
+++ b/mr-dashboards/mr2025/resources/MetadataFailingValidationAllEndpoints.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_31054221BAC41EB9732488F3BE13EDC387331D6C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B740085-E7A4-4B9A-B77C-F7E670FEF4AA}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monacve\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE0B6EAD-0E86-498B-9A09-0498B76EC938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="1" r:id="rId1"/>
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="197">
   <si>
     <t>md_failed</t>
   </si>
@@ -624,13 +629,16 @@
   </si>
   <si>
     <t>eafc8b78-0f9c-4e2e-a754-c2624fb84ce7</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -677,6 +685,20 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -699,7 +721,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -707,6 +729,8 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -794,9 +818,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -834,7 +858,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -940,7 +964,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1082,7 +1106,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1091,14 +1115,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C51"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="56.85546875" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="56.81640625" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="95" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1106,7 +1130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1114,7 +1138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="1" customFormat="1">
+    <row r="4" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1125,7 +1149,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1136,7 +1160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -1147,7 +1171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -1158,7 +1182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
@@ -1169,7 +1193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
@@ -1180,7 +1204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
@@ -1191,7 +1215,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
@@ -1202,7 +1226,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
@@ -1213,7 +1237,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
@@ -1224,7 +1248,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
@@ -1235,7 +1259,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>37</v>
       </c>
@@ -1246,7 +1270,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>40</v>
       </c>
@@ -1257,7 +1281,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
@@ -1268,7 +1292,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>46</v>
       </c>
@@ -1279,7 +1303,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>49</v>
       </c>
@@ -1290,7 +1314,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>52</v>
       </c>
@@ -1301,7 +1325,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>55</v>
       </c>
@@ -1312,7 +1336,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>58</v>
       </c>
@@ -1323,7 +1347,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>61</v>
       </c>
@@ -1334,7 +1358,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>64</v>
       </c>
@@ -1345,7 +1369,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>1.1000000000000001</v>
       </c>
@@ -1356,7 +1380,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>1.2</v>
       </c>
@@ -1367,7 +1391,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>1.3</v>
       </c>
@@ -1378,7 +1402,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>1.4</v>
       </c>
@@ -1389,7 +1413,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>1.5</v>
       </c>
@@ -1400,7 +1424,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>1.6</v>
       </c>
@@ -1411,7 +1435,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>1.7</v>
       </c>
@@ -1422,7 +1446,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>1.8</v>
       </c>
@@ -1433,7 +1457,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>1.9</v>
       </c>
@@ -1444,7 +1468,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>85</v>
       </c>
@@ -1455,7 +1479,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>1.1100000000000001</v>
       </c>
@@ -1466,7 +1490,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>3.1</v>
       </c>
@@ -1477,7 +1501,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>3.2</v>
       </c>
@@ -1488,7 +1512,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>3.3</v>
       </c>
@@ -1499,7 +1523,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>3.4</v>
       </c>
@@ -1510,7 +1534,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>3.5</v>
       </c>
@@ -1521,7 +1545,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>3.6</v>
       </c>
@@ -1532,7 +1556,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>3.7</v>
       </c>
@@ -1543,7 +1567,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>3.8</v>
       </c>
@@ -1554,7 +1578,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>4.0999999999999996</v>
       </c>
@@ -1565,7 +1589,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>5.0999999999999996</v>
       </c>
@@ -1576,7 +1600,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>5.2</v>
       </c>
@@ -1587,7 +1611,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>5.3</v>
       </c>
@@ -1598,7 +1622,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>5.4</v>
       </c>
@@ -1609,7 +1633,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>5.5</v>
       </c>
@@ -1620,7 +1644,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>118</v>
       </c>
@@ -1631,7 +1655,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>121</v>
       </c>
@@ -1660,17 +1684,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK36"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1" collapsed="1"/>
-    <col min="5" max="37" width="6.5703125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="15.26953125" style="8" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="37.26953125" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.54296875" customWidth="1" collapsed="1"/>
+    <col min="5" max="37" width="6.54296875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1782,2499 +1806,2499 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="2" spans="1:37">
-      <c r="A2" t="s">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>2</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>3</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3">
+        <v>44</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>43</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>43</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" t="s">
         <v>127</v>
       </c>
-      <c r="C2">
+      <c r="C5">
         <v>194</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>179</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
         <v>2</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
         <v>7</v>
       </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
         <v>2</v>
       </c>
-      <c r="AE2">
+      <c r="AE5">
         <v>2</v>
       </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>1</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>1</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
-      <c r="A3" t="s">
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6">
+        <v>29</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7">
         <v>128</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>36</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>52</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>42</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>25</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>27</v>
+      </c>
+      <c r="T7">
+        <v>6</v>
+      </c>
+      <c r="U7">
+        <v>5</v>
+      </c>
+      <c r="V7">
+        <v>3</v>
+      </c>
+      <c r="W7">
+        <v>4</v>
+      </c>
+      <c r="X7">
+        <v>6</v>
+      </c>
+      <c r="Y7">
+        <v>41</v>
+      </c>
+      <c r="Z7">
+        <v>41</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
+      </c>
+      <c r="AB7">
+        <v>2</v>
+      </c>
+      <c r="AC7">
+        <v>9</v>
+      </c>
+      <c r="AD7">
+        <v>49</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>6</v>
+      </c>
+      <c r="AG7">
+        <v>6</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>3</v>
+      </c>
+      <c r="AJ7">
+        <v>7</v>
+      </c>
+      <c r="AK7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8">
+        <v>43</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>42</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>43</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>43</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>5</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>29</v>
+      </c>
+      <c r="AD8">
+        <v>5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>43</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>43</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>2</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10">
+        <v>34391</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>131</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>40</v>
+      </c>
+      <c r="L10">
+        <v>226</v>
+      </c>
+      <c r="M10">
+        <v>10</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>13</v>
+      </c>
+      <c r="P10">
+        <v>280</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>820</v>
+      </c>
+      <c r="S10">
+        <v>32430</v>
+      </c>
+      <c r="T10">
+        <v>934</v>
+      </c>
+      <c r="U10">
+        <v>122</v>
+      </c>
+      <c r="V10">
+        <v>5</v>
+      </c>
+      <c r="W10">
+        <v>6</v>
+      </c>
+      <c r="X10">
+        <v>7</v>
+      </c>
+      <c r="Y10">
+        <v>942</v>
+      </c>
+      <c r="Z10">
+        <v>13</v>
+      </c>
+      <c r="AA10">
+        <v>3</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>54</v>
+      </c>
+      <c r="AE10">
+        <v>459</v>
+      </c>
+      <c r="AF10">
+        <v>100</v>
+      </c>
+      <c r="AG10">
+        <v>12</v>
+      </c>
+      <c r="AH10">
+        <v>53</v>
+      </c>
+      <c r="AI10">
+        <v>10</v>
+      </c>
+      <c r="AJ10">
+        <v>89</v>
+      </c>
+      <c r="AK10">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11">
+        <v>62</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>28</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>3</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>4</v>
+      </c>
+      <c r="S11">
+        <v>38</v>
+      </c>
+      <c r="T11">
+        <v>17</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>16</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>4</v>
+      </c>
+      <c r="AD11">
+        <v>3</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>21</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>7</v>
+      </c>
+      <c r="AK11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" t="s">
         <v>129</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37">
-      <c r="A4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4">
-        <v>121</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>9</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16">
+        <v>88</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>36</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>29</v>
+      </c>
+      <c r="H16">
+        <v>22</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>15</v>
+      </c>
+      <c r="M16">
+        <v>4</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>10</v>
+      </c>
+      <c r="Q16">
+        <v>28</v>
+      </c>
+      <c r="R16">
+        <v>11</v>
+      </c>
+      <c r="S16">
+        <v>65</v>
+      </c>
+      <c r="T16">
+        <v>34</v>
+      </c>
+      <c r="U16">
+        <v>3</v>
+      </c>
+      <c r="V16">
+        <v>16</v>
+      </c>
+      <c r="W16">
+        <v>16</v>
+      </c>
+      <c r="X16">
+        <v>17</v>
+      </c>
+      <c r="Y16">
+        <v>12</v>
+      </c>
+      <c r="Z16">
+        <v>33</v>
+      </c>
+      <c r="AA16">
+        <v>1</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>16</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>36</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>1</v>
+      </c>
+      <c r="AI16">
+        <v>19</v>
+      </c>
+      <c r="AJ16">
+        <v>21</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18">
         <v>48</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>11</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>11</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>2</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>4</v>
+      </c>
+      <c r="R18">
+        <v>12</v>
+      </c>
+      <c r="S18">
+        <v>38</v>
+      </c>
+      <c r="T18">
+        <v>10</v>
+      </c>
+      <c r="U18">
+        <v>6</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>9</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>10</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>15</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>1</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>9</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20">
+        <v>24</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
         <v>3</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
         <v>2</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="S20">
+        <v>7</v>
+      </c>
+      <c r="T20">
+        <v>3</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>3</v>
+      </c>
+      <c r="Y20">
+        <v>3</v>
+      </c>
+      <c r="Z20">
+        <v>4</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>5</v>
+      </c>
+      <c r="AE20">
+        <v>1</v>
+      </c>
+      <c r="AF20">
+        <v>1</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>2</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>5</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21">
+        <v>874</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>7</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>13</v>
+      </c>
+      <c r="S21">
+        <v>6</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>744</v>
+      </c>
+      <c r="Z21">
         <v>51</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>69</v>
-      </c>
-      <c r="Z4">
-        <v>75</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>18</v>
-      </c>
-      <c r="AD4">
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>169</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>2</v>
+      </c>
+      <c r="AH21">
+        <v>17</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B22" t="s">
+        <v>187</v>
+      </c>
+      <c r="C22">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>11</v>
+      </c>
+      <c r="T22">
         <v>10</v>
       </c>
-      <c r="AE4">
-        <v>27</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>3</v>
-      </c>
-      <c r="AH4">
-        <v>1</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>1</v>
-      </c>
-      <c r="AK4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37">
-      <c r="A5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5">
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>1</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37">
-      <c r="A6" t="s">
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>2</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B23" t="s">
         <v>135</v>
       </c>
-      <c r="C6">
+      <c r="C23">
         <v>2</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>2</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
-      <c r="A7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>3</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>1</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37">
-      <c r="A8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>21</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>23</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>21</v>
-      </c>
-      <c r="K8">
-        <v>21</v>
-      </c>
-      <c r="L8">
-        <v>21</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>21</v>
-      </c>
-      <c r="Z8">
-        <v>3</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37">
-      <c r="A9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9">
-        <v>44</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>43</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>43</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>1</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37">
-      <c r="A10" t="s">
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B24" t="s">
         <v>143</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37">
-      <c r="A11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11">
-        <v>88</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>36</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>29</v>
-      </c>
-      <c r="H11">
-        <v>22</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>15</v>
-      </c>
-      <c r="M11">
-        <v>4</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>10</v>
-      </c>
-      <c r="Q11">
-        <v>28</v>
-      </c>
-      <c r="R11">
-        <v>11</v>
-      </c>
-      <c r="S11">
-        <v>65</v>
-      </c>
-      <c r="T11">
-        <v>34</v>
-      </c>
-      <c r="U11">
-        <v>3</v>
-      </c>
-      <c r="V11">
-        <v>16</v>
-      </c>
-      <c r="W11">
-        <v>16</v>
-      </c>
-      <c r="X11">
-        <v>17</v>
-      </c>
-      <c r="Y11">
-        <v>12</v>
-      </c>
-      <c r="Z11">
-        <v>33</v>
-      </c>
-      <c r="AA11">
-        <v>1</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>16</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>36</v>
-      </c>
-      <c r="AG11">
-        <v>1</v>
-      </c>
-      <c r="AH11">
-        <v>1</v>
-      </c>
-      <c r="AI11">
-        <v>19</v>
-      </c>
-      <c r="AJ11">
-        <v>21</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37">
-      <c r="A12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12">
-        <v>62</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>28</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>3</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>4</v>
-      </c>
-      <c r="S12">
-        <v>38</v>
-      </c>
-      <c r="T12">
-        <v>17</v>
-      </c>
-      <c r="U12">
-        <v>1</v>
-      </c>
-      <c r="V12">
-        <v>1</v>
-      </c>
-      <c r="W12">
-        <v>1</v>
-      </c>
-      <c r="X12">
-        <v>1</v>
-      </c>
-      <c r="Y12">
-        <v>16</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>4</v>
-      </c>
-      <c r="AD12">
-        <v>3</v>
-      </c>
-      <c r="AE12">
-        <v>1</v>
-      </c>
-      <c r="AF12">
-        <v>1</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>21</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>7</v>
-      </c>
-      <c r="AK12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37">
-      <c r="A13" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37">
-      <c r="A14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C14">
-        <v>43</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>42</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>43</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>43</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>1</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>5</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>29</v>
-      </c>
-      <c r="AD14">
-        <v>5</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>43</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>43</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37">
-      <c r="A15" t="s">
-        <v>152</v>
-      </c>
-      <c r="B15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>1</v>
-      </c>
-      <c r="AB15">
-        <v>1</v>
-      </c>
-      <c r="AC15">
-        <v>0</v>
-      </c>
-      <c r="AD15">
-        <v>1</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>1</v>
-      </c>
-      <c r="AG15">
-        <v>1</v>
-      </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <v>1</v>
-      </c>
-      <c r="AJ15">
-        <v>2</v>
-      </c>
-      <c r="AK15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
-      <c r="A16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16">
-        <v>8</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>2</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37">
-      <c r="A17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B17" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17">
-        <v>40</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>3</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>8</v>
-      </c>
-      <c r="T17">
-        <v>1</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>3</v>
-      </c>
-      <c r="W17">
-        <v>3</v>
-      </c>
-      <c r="X17">
-        <v>3</v>
-      </c>
-      <c r="Y17">
-        <v>6</v>
-      </c>
-      <c r="Z17">
-        <v>8</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>6</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>1</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>7</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37">
-      <c r="A18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18">
-        <v>874</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>7</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>13</v>
-      </c>
-      <c r="S18">
-        <v>6</v>
-      </c>
-      <c r="T18">
-        <v>1</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>744</v>
-      </c>
-      <c r="Z18">
-        <v>51</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>169</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>2</v>
-      </c>
-      <c r="AH18">
-        <v>17</v>
-      </c>
-      <c r="AI18">
-        <v>0</v>
-      </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37">
-      <c r="A19" t="s">
-        <v>160</v>
-      </c>
-      <c r="B19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C19">
-        <v>34391</v>
-      </c>
-      <c r="D19">
-        <v>5</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>6</v>
-      </c>
-      <c r="H19">
-        <v>131</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>40</v>
-      </c>
-      <c r="L19">
-        <v>226</v>
-      </c>
-      <c r="M19">
-        <v>10</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>13</v>
-      </c>
-      <c r="P19">
-        <v>280</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>820</v>
-      </c>
-      <c r="S19">
-        <v>32430</v>
-      </c>
-      <c r="T19">
-        <v>934</v>
-      </c>
-      <c r="U19">
-        <v>122</v>
-      </c>
-      <c r="V19">
-        <v>5</v>
-      </c>
-      <c r="W19">
-        <v>6</v>
-      </c>
-      <c r="X19">
-        <v>7</v>
-      </c>
-      <c r="Y19">
-        <v>942</v>
-      </c>
-      <c r="Z19">
-        <v>13</v>
-      </c>
-      <c r="AA19">
-        <v>3</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>1</v>
-      </c>
-      <c r="AD19">
-        <v>54</v>
-      </c>
-      <c r="AE19">
-        <v>459</v>
-      </c>
-      <c r="AF19">
-        <v>100</v>
-      </c>
-      <c r="AG19">
-        <v>12</v>
-      </c>
-      <c r="AH19">
-        <v>53</v>
-      </c>
-      <c r="AI19">
-        <v>10</v>
-      </c>
-      <c r="AJ19">
-        <v>89</v>
-      </c>
-      <c r="AK19">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37">
-      <c r="A20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C20">
-        <v>50</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>27</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>1</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>17</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20">
-        <v>0</v>
-      </c>
-      <c r="AI20">
-        <v>0</v>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:37">
-      <c r="A21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B21" t="s">
-        <v>165</v>
-      </c>
-      <c r="C21">
-        <v>6</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>2</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>1</v>
-      </c>
-      <c r="AD21">
-        <v>3</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:37">
-      <c r="A22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B22" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22">
-        <v>29</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>25</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22">
-        <v>1</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>1</v>
-      </c>
-      <c r="AH22">
-        <v>0</v>
-      </c>
-      <c r="AI22">
-        <v>0</v>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:37">
-      <c r="A23" t="s">
-        <v>168</v>
-      </c>
-      <c r="B23" t="s">
-        <v>169</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <v>0</v>
-      </c>
-      <c r="AI23">
-        <v>0</v>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:37">
-      <c r="A24" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" t="s">
-        <v>171</v>
-      </c>
       <c r="C24">
         <v>0</v>
       </c>
@@ -4381,8 +4405,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:37">
-      <c r="A25" t="s">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
         <v>172</v>
       </c>
       <c r="B25" t="s">
@@ -4494,991 +4518,991 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:37">
-      <c r="A26" t="s">
-        <v>174</v>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="C26">
+        <v>121</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
         <v>48</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>2</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>51</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>69</v>
+      </c>
+      <c r="Z26">
+        <v>75</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>18</v>
+      </c>
+      <c r="AD26">
+        <v>10</v>
+      </c>
+      <c r="AE26">
+        <v>27</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>3</v>
+      </c>
+      <c r="AH26">
+        <v>1</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>1</v>
+      </c>
+      <c r="AK26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A28" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28">
+        <v>40</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>3</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>8</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>3</v>
+      </c>
+      <c r="W28">
+        <v>3</v>
+      </c>
+      <c r="X28">
+        <v>3</v>
+      </c>
+      <c r="Y28">
+        <v>6</v>
+      </c>
+      <c r="Z28">
+        <v>8</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>6</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>1</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>7</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B29" t="s">
+        <v>195</v>
+      </c>
+      <c r="C29">
+        <v>28</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>2</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>1</v>
+      </c>
+      <c r="AE29">
+        <v>2</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>1</v>
+      </c>
+      <c r="AK29">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30">
+        <v>23</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>21</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>23</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>21</v>
+      </c>
+      <c r="K30">
+        <v>21</v>
+      </c>
+      <c r="L30">
+        <v>21</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>21</v>
+      </c>
+      <c r="Z30">
+        <v>3</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C31">
+        <v>47</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>13</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
         <v>11</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>2</v>
+      </c>
+      <c r="T31">
+        <v>2</v>
+      </c>
+      <c r="U31">
+        <v>6</v>
+      </c>
+      <c r="V31">
         <v>11</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
+      <c r="W31">
+        <v>11</v>
+      </c>
+      <c r="X31">
+        <v>11</v>
+      </c>
+      <c r="Y31">
+        <v>5</v>
+      </c>
+      <c r="Z31">
+        <v>6</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>6</v>
+      </c>
+      <c r="AE31">
         <v>2</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>1</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>13</v>
+      </c>
+      <c r="AK31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32">
+        <v>50</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>5</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>3</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>1</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33">
+        <v>50</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>27</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>17</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B34" t="s">
+        <v>183</v>
+      </c>
+      <c r="C34">
+        <v>34</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>30</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>31</v>
+      </c>
+      <c r="T34">
+        <v>25</v>
+      </c>
+      <c r="U34">
         <v>4</v>
       </c>
-      <c r="R26">
-        <v>12</v>
-      </c>
-      <c r="S26">
-        <v>38</v>
-      </c>
-      <c r="T26">
-        <v>10</v>
-      </c>
-      <c r="U26">
-        <v>6</v>
-      </c>
-      <c r="V26">
-        <v>1</v>
-      </c>
-      <c r="W26">
-        <v>1</v>
-      </c>
-      <c r="X26">
-        <v>9</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>10</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>3</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>15</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26">
-        <v>1</v>
-      </c>
-      <c r="AI26">
-        <v>0</v>
-      </c>
-      <c r="AJ26">
-        <v>9</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:37">
-      <c r="A27" t="s">
-        <v>176</v>
-      </c>
-      <c r="B27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C27">
-        <v>47</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>13</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>11</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>2</v>
-      </c>
-      <c r="T27">
-        <v>2</v>
-      </c>
-      <c r="U27">
-        <v>6</v>
-      </c>
-      <c r="V27">
-        <v>11</v>
-      </c>
-      <c r="W27">
-        <v>11</v>
-      </c>
-      <c r="X27">
-        <v>11</v>
-      </c>
-      <c r="Y27">
+      <c r="V34">
         <v>5</v>
       </c>
-      <c r="Z27">
-        <v>6</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>6</v>
-      </c>
-      <c r="AE27">
-        <v>2</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>1</v>
-      </c>
-      <c r="AH27">
-        <v>0</v>
-      </c>
-      <c r="AI27">
-        <v>0</v>
-      </c>
-      <c r="AJ27">
-        <v>13</v>
-      </c>
-      <c r="AK27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:37">
-      <c r="A28" t="s">
-        <v>178</v>
-      </c>
-      <c r="B28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:37">
-      <c r="A29" t="s">
-        <v>180</v>
-      </c>
-      <c r="B29" t="s">
-        <v>181</v>
-      </c>
-      <c r="C29">
-        <v>417</v>
-      </c>
-      <c r="D29">
-        <v>13</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>220</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>16</v>
-      </c>
-      <c r="M29">
-        <v>19</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>4</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>3</v>
-      </c>
-      <c r="R29">
-        <v>78</v>
-      </c>
-      <c r="S29">
-        <v>415</v>
-      </c>
-      <c r="T29">
-        <v>169</v>
-      </c>
-      <c r="U29">
-        <v>4</v>
-      </c>
-      <c r="V29">
-        <v>397</v>
-      </c>
-      <c r="W29">
-        <v>397</v>
-      </c>
-      <c r="X29">
-        <v>410</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>13</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <v>68</v>
-      </c>
-      <c r="AD29">
-        <v>191</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>3</v>
-      </c>
-      <c r="AH29">
-        <v>9</v>
-      </c>
-      <c r="AI29">
-        <v>156</v>
-      </c>
-      <c r="AJ29">
-        <v>412</v>
-      </c>
-      <c r="AK29">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:37">
-      <c r="A30" t="s">
-        <v>182</v>
-      </c>
-      <c r="B30" t="s">
-        <v>183</v>
-      </c>
-      <c r="C30">
-        <v>34</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>30</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
+      <c r="W34">
         <v>5</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>1</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>1</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>31</v>
-      </c>
-      <c r="T30">
-        <v>25</v>
-      </c>
-      <c r="U30">
-        <v>4</v>
-      </c>
-      <c r="V30">
+      <c r="X34">
         <v>5</v>
       </c>
-      <c r="W30">
-        <v>5</v>
-      </c>
-      <c r="X30">
-        <v>5</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>5</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AI30">
-        <v>0</v>
-      </c>
-      <c r="AJ30">
-        <v>6</v>
-      </c>
-      <c r="AK30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:37">
-      <c r="A31" t="s">
-        <v>184</v>
-      </c>
-      <c r="B31" t="s">
-        <v>185</v>
-      </c>
-      <c r="C31">
-        <v>128</v>
-      </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31">
-        <v>36</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31">
-        <v>52</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>2</v>
-      </c>
-      <c r="K31">
-        <v>2</v>
-      </c>
-      <c r="L31">
-        <v>42</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>25</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>27</v>
-      </c>
-      <c r="T31">
-        <v>6</v>
-      </c>
-      <c r="U31">
-        <v>5</v>
-      </c>
-      <c r="V31">
-        <v>3</v>
-      </c>
-      <c r="W31">
-        <v>4</v>
-      </c>
-      <c r="X31">
-        <v>6</v>
-      </c>
-      <c r="Y31">
-        <v>41</v>
-      </c>
-      <c r="Z31">
-        <v>41</v>
-      </c>
-      <c r="AA31">
-        <v>3</v>
-      </c>
-      <c r="AB31">
-        <v>2</v>
-      </c>
-      <c r="AC31">
-        <v>9</v>
-      </c>
-      <c r="AD31">
-        <v>49</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>6</v>
-      </c>
-      <c r="AG31">
-        <v>6</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AI31">
-        <v>3</v>
-      </c>
-      <c r="AJ31">
-        <v>7</v>
-      </c>
-      <c r="AK31">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:37">
-      <c r="A32" t="s">
-        <v>186</v>
-      </c>
-      <c r="B32" t="s">
-        <v>187</v>
-      </c>
-      <c r="C32">
-        <v>15</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>1</v>
-      </c>
-      <c r="S32">
-        <v>11</v>
-      </c>
-      <c r="T32">
-        <v>10</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>1</v>
-      </c>
-      <c r="W32">
-        <v>1</v>
-      </c>
-      <c r="X32">
-        <v>2</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>1</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>2</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:37">
-      <c r="A33" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" t="s">
-        <v>189</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
-      </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
-      </c>
-      <c r="AB33">
-        <v>0</v>
-      </c>
-      <c r="AC33">
-        <v>0</v>
-      </c>
-      <c r="AD33">
-        <v>0</v>
-      </c>
-      <c r="AE33">
-        <v>0</v>
-      </c>
-      <c r="AF33">
-        <v>0</v>
-      </c>
-      <c r="AG33">
-        <v>0</v>
-      </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
-      <c r="AI33">
-        <v>0</v>
-      </c>
-      <c r="AJ33">
-        <v>0</v>
-      </c>
-      <c r="AK33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:37">
-      <c r="A34" t="s">
-        <v>190</v>
-      </c>
-      <c r="B34" t="s">
-        <v>191</v>
-      </c>
-      <c r="C34">
-        <v>24</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>3</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>4</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>1</v>
-      </c>
-      <c r="Q34">
-        <v>1</v>
-      </c>
-      <c r="R34">
-        <v>2</v>
-      </c>
-      <c r="S34">
-        <v>7</v>
-      </c>
-      <c r="T34">
-        <v>3</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>1</v>
-      </c>
-      <c r="W34">
-        <v>1</v>
-      </c>
-      <c r="X34">
-        <v>3</v>
-      </c>
       <c r="Y34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34">
         <v>0</v>
@@ -5490,254 +5514,289 @@
         <v>5</v>
       </c>
       <c r="AE34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34">
         <v>0</v>
       </c>
       <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>6</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35">
+        <v>5</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>1</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>1</v>
+      </c>
+      <c r="AB35">
+        <v>1</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>1</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>1</v>
+      </c>
+      <c r="AG35">
+        <v>1</v>
+      </c>
+      <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <v>1</v>
+      </c>
+      <c r="AJ35">
         <v>2</v>
       </c>
-      <c r="AI34">
-        <v>0</v>
-      </c>
-      <c r="AJ34">
-        <v>5</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:37">
-      <c r="A35" t="s">
-        <v>192</v>
-      </c>
-      <c r="B35" t="s">
-        <v>193</v>
-      </c>
-      <c r="C35">
-        <v>10</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>1</v>
-      </c>
-      <c r="U35">
-        <v>1</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
-      <c r="AG35">
+      <c r="AK35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A36" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36">
+        <f>SUM(C2:C35)</f>
+        <v>36367</v>
+      </c>
+      <c r="D36">
+        <f t="shared" ref="D36:AK36" si="0">SUM(D2:D35)</f>
+        <v>11</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="0"/>
+        <v>555</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="0"/>
+        <v>236</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="0"/>
+        <v>310</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P36">
+        <f t="shared" si="0"/>
+        <v>331</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="0"/>
+        <v>865</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="0"/>
+        <v>32763</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="0"/>
+        <v>1046</v>
+      </c>
+      <c r="U36">
+        <f t="shared" si="0"/>
+        <v>152</v>
+      </c>
+      <c r="V36">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="W36">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="X36">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="Y36">
+        <f t="shared" si="0"/>
+        <v>1876</v>
+      </c>
+      <c r="Z36">
+        <f t="shared" si="0"/>
+        <v>261</v>
+      </c>
+      <c r="AA36">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="AH35">
-        <v>0</v>
-      </c>
-      <c r="AI35">
-        <v>0</v>
-      </c>
-      <c r="AJ35">
-        <v>0</v>
-      </c>
-      <c r="AK35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:37">
-      <c r="A36" t="s">
-        <v>194</v>
-      </c>
-      <c r="B36" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36">
-        <v>28</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
+      <c r="AB36">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>2</v>
-      </c>
-      <c r="V36">
-        <v>0</v>
-      </c>
-      <c r="W36">
-        <v>0</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>0</v>
-      </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-      <c r="AA36">
-        <v>0</v>
-      </c>
-      <c r="AB36">
-        <v>0</v>
-      </c>
       <c r="AC36">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>63</v>
       </c>
       <c r="AD36">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>340</v>
       </c>
       <c r="AE36">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>494</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>204</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>36</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>98</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>33</v>
       </c>
       <c r="AJ36">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>217</v>
       </c>
       <c r="AK36">
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AK36">
+    <sortCondition ref="A1:A36"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -5746,15 +5805,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AK36"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1" collapsed="1"/>
-    <col min="4" max="37" width="6.5703125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="8.54296875" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="12.1796875" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1" collapsed="1"/>
+    <col min="4" max="37" width="6.54296875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="15">
+    <row r="1" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
@@ -5867,7 +5926,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -5980,7 +6039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>128</v>
       </c>
@@ -6093,7 +6152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -6206,7 +6265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>132</v>
       </c>
@@ -6319,7 +6378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>134</v>
       </c>
@@ -6432,7 +6491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -6545,7 +6604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>138</v>
       </c>
@@ -6658,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>140</v>
       </c>
@@ -6771,7 +6830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>142</v>
       </c>
@@ -6884,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -6997,7 +7056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>146</v>
       </c>
@@ -7110,7 +7169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>148</v>
       </c>
@@ -7223,7 +7282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>150</v>
       </c>
@@ -7336,7 +7395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>152</v>
       </c>
@@ -7449,7 +7508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>154</v>
       </c>
@@ -7562,7 +7621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>156</v>
       </c>
@@ -7675,7 +7734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:37">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>158</v>
       </c>
@@ -7788,7 +7847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:37">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>160</v>
       </c>
@@ -7901,7 +7960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:37">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>162</v>
       </c>
@@ -8014,7 +8073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>164</v>
       </c>
@@ -8127,7 +8186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:37">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>166</v>
       </c>
@@ -8240,7 +8299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:37">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>168</v>
       </c>
@@ -8353,7 +8412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:37">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>170</v>
       </c>
@@ -8466,7 +8525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:37">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>172</v>
       </c>
@@ -8579,7 +8638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:37">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>174</v>
       </c>
@@ -8692,7 +8751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:37">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>176</v>
       </c>
@@ -8805,7 +8864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:37">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>178</v>
       </c>
@@ -8918,7 +8977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:37">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>180</v>
       </c>
@@ -9031,7 +9090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:37">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -9144,7 +9203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:37">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>184</v>
       </c>
@@ -9257,7 +9316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:37">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>186</v>
       </c>
@@ -9370,7 +9429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:37">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>188</v>
       </c>
@@ -9483,7 +9542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:37">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>190</v>
       </c>
@@ -9596,7 +9655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:37">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>192</v>
       </c>
@@ -9709,7 +9768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:37">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>194</v>
       </c>

--- a/mr-dashboards/mr2025/resources/MetadataFailingValidationAllEndpoints.xlsx
+++ b/mr-dashboards/mr2025/resources/MetadataFailingValidationAllEndpoints.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\monacve\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE0B6EAD-0E86-498B-9A09-0498B76EC938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD4AE9B-44BE-433D-BDB0-68DA09ED53FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="195">
   <si>
     <t>md_failed</t>
   </si>
@@ -581,12 +581,6 @@
   </si>
   <si>
     <t>04e44bbf-163c-42fa-ab6c-a2114c1eee5b</t>
-  </si>
-  <si>
-    <t>CH</t>
-  </si>
-  <si>
-    <t>864dd8d5-5e47-47b4-8115-9675d62d316e</t>
   </si>
   <si>
     <t>SI</t>
@@ -2373,10 +2367,10 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C7">
         <v>128</v>
@@ -3164,10 +3158,10 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -3729,10 +3723,10 @@
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3842,10 +3836,10 @@
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C20">
         <v>24</v>
@@ -4068,10 +4062,10 @@
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B22" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C22">
         <v>15</v>
@@ -4859,10 +4853,10 @@
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B29" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C29">
         <v>28</v>
@@ -5424,10 +5418,10 @@
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C34">
         <v>34</v>
@@ -5650,7 +5644,7 @@
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C36">
         <f>SUM(C2:C35)</f>
@@ -5804,17 +5798,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AK36"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.54296875" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="16" style="8" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="12.1796875" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="10.54296875" customWidth="1" collapsed="1"/>
     <col min="4" max="37" width="6.54296875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -5927,2503 +5921,2503 @@
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2">
+        <v>241</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>36</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>238</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>2</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" t="s">
         <v>127</v>
       </c>
-      <c r="C2">
+      <c r="C5">
         <v>52</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>15</v>
       </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
         <v>6</v>
       </c>
-      <c r="AD2">
+      <c r="AD5">
         <v>31</v>
       </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>10</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>20</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>3</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>2</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>2</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8">
+        <v>62</v>
+      </c>
+      <c r="D8">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>62</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>62</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>62</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>9</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>62</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <v>4</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>6</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10">
+        <v>71378</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>19</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>11</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>18</v>
+      </c>
+      <c r="R10">
+        <v>61185</v>
+      </c>
+      <c r="S10">
+        <v>97</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>12</v>
+      </c>
+      <c r="V10">
+        <v>12</v>
+      </c>
+      <c r="W10">
+        <v>12</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>16</v>
+      </c>
+      <c r="AB10">
+        <v>5</v>
+      </c>
+      <c r="AC10">
+        <v>12373</v>
+      </c>
+      <c r="AD10">
+        <v>69</v>
+      </c>
+      <c r="AE10">
+        <v>699</v>
+      </c>
+      <c r="AF10">
+        <v>5</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>5</v>
+      </c>
+      <c r="S11">
+        <v>3</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>2</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>2</v>
+      </c>
+      <c r="AC11">
+        <v>31</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>2</v>
+      </c>
+      <c r="AF11">
+        <v>2</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B12" t="s">
         <v>129</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4">
-        <v>37</v>
-      </c>
-      <c r="D4">
-        <v>15</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14">
+        <v>112</v>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>3</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>2</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>13</v>
+      </c>
+      <c r="AB14">
+        <v>2</v>
+      </c>
+      <c r="AC14">
+        <v>104</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>2</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16">
+        <v>23</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>6</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>9</v>
+      </c>
+      <c r="S16">
+        <v>2</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>2</v>
+      </c>
+      <c r="V16">
+        <v>2</v>
+      </c>
+      <c r="W16">
+        <v>2</v>
+      </c>
+      <c r="X16">
+        <v>9</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>9</v>
+      </c>
+      <c r="AB16">
+        <v>7</v>
+      </c>
+      <c r="AC16">
+        <v>19</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>9</v>
+      </c>
+      <c r="AF16">
+        <v>7</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>6</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
         <v>5</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>12</v>
-      </c>
-      <c r="S4">
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>19</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B20" t="s">
+        <v>189</v>
+      </c>
+      <c r="C20">
+        <v>25</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
         <v>2</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>11</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>12</v>
-      </c>
-      <c r="AD4">
-        <v>1</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5">
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>19</v>
+      </c>
+      <c r="AC20">
+        <v>8</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>19</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21">
+        <v>301</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>10</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>288</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>1</v>
+      </c>
+      <c r="AJ21">
+        <v>2</v>
+      </c>
+      <c r="AK21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B22" t="s">
         <v>185</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>1</v>
+      </c>
+      <c r="AC22">
         <v>2</v>
       </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>185</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>1</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>1</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>1</v>
+      </c>
+      <c r="AK22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B23" t="s">
         <v>135</v>
       </c>
-      <c r="C6">
+      <c r="C23">
         <v>4</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
         <v>4</v>
       </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
         <v>2</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7">
-        <v>17</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>17</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8">
-        <v>112</v>
-      </c>
-      <c r="D8">
-        <v>84</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>87</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>84</v>
-      </c>
-      <c r="J8">
-        <v>84</v>
-      </c>
-      <c r="K8">
-        <v>84</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>27</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B24" t="s">
         <v>143</v>
-      </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>4</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11">
-        <v>23</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>4</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>6</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>9</v>
-      </c>
-      <c r="S11">
-        <v>2</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>2</v>
-      </c>
-      <c r="V11">
-        <v>2</v>
-      </c>
-      <c r="W11">
-        <v>2</v>
-      </c>
-      <c r="X11">
-        <v>9</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>9</v>
-      </c>
-      <c r="AB11">
-        <v>7</v>
-      </c>
-      <c r="AC11">
-        <v>19</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>9</v>
-      </c>
-      <c r="AF11">
-        <v>7</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12">
-        <v>40</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>5</v>
-      </c>
-      <c r="S12">
-        <v>3</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>2</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>1</v>
-      </c>
-      <c r="AB12">
-        <v>2</v>
-      </c>
-      <c r="AC12">
-        <v>31</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>2</v>
-      </c>
-      <c r="AF12">
-        <v>2</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C13">
-        <v>8</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>6</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C14">
-        <v>62</v>
-      </c>
-      <c r="D14">
-        <v>23</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>62</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>62</v>
-      </c>
-      <c r="S14">
-        <v>1</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>62</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>9</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>62</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>152</v>
-      </c>
-      <c r="B15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15">
-        <v>21</v>
-      </c>
-      <c r="D15">
-        <v>5</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>0</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
-      </c>
-      <c r="Z15">
-        <v>0</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0</v>
-      </c>
-      <c r="AC15">
-        <v>1</v>
-      </c>
-      <c r="AD15">
-        <v>0</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>0</v>
-      </c>
-      <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AH15">
-        <v>0</v>
-      </c>
-      <c r="AI15">
-        <v>0</v>
-      </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
-      <c r="AK15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16">
-        <v>13</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>2</v>
-      </c>
-      <c r="P16">
-        <v>4</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>6</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B17" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17">
-        <v>21</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>2</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>14</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18">
-        <v>301</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>10</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>288</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>0</v>
-      </c>
-      <c r="AH18">
-        <v>0</v>
-      </c>
-      <c r="AI18">
-        <v>1</v>
-      </c>
-      <c r="AJ18">
-        <v>2</v>
-      </c>
-      <c r="AK18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>160</v>
-      </c>
-      <c r="B19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C19">
-        <v>71378</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>19</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>2</v>
-      </c>
-      <c r="N19">
-        <v>11</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>18</v>
-      </c>
-      <c r="R19">
-        <v>61185</v>
-      </c>
-      <c r="S19">
-        <v>97</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>12</v>
-      </c>
-      <c r="V19">
-        <v>12</v>
-      </c>
-      <c r="W19">
-        <v>12</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>16</v>
-      </c>
-      <c r="AB19">
-        <v>5</v>
-      </c>
-      <c r="AC19">
-        <v>12373</v>
-      </c>
-      <c r="AD19">
-        <v>69</v>
-      </c>
-      <c r="AE19">
-        <v>699</v>
-      </c>
-      <c r="AF19">
-        <v>5</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AI19">
-        <v>0</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C20">
-        <v>24</v>
-      </c>
-      <c r="D20">
-        <v>8</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>1</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>7</v>
-      </c>
-      <c r="AB20">
-        <v>1</v>
-      </c>
-      <c r="AC20">
-        <v>14</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>1</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20">
-        <v>0</v>
-      </c>
-      <c r="AI20">
-        <v>0</v>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B21" t="s">
-        <v>165</v>
-      </c>
-      <c r="C21">
-        <v>241</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>1</v>
-      </c>
-      <c r="Q21">
-        <v>1</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>36</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>238</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B22" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22">
-        <v>0</v>
-      </c>
-      <c r="AI22">
-        <v>0</v>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>168</v>
-      </c>
-      <c r="B23" t="s">
-        <v>169</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23">
-        <v>0</v>
-      </c>
-      <c r="AI23">
-        <v>0</v>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>170</v>
-      </c>
-      <c r="B24" t="s">
-        <v>171</v>
       </c>
       <c r="C24">
         <v>5</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -8498,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="AC24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -8526,7 +8520,7 @@
       </c>
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="A25" s="8" t="s">
         <v>172</v>
       </c>
       <c r="B25" t="s">
@@ -8639,627 +8633,627 @@
       </c>
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>174</v>
+      <c r="A26" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="C26">
+        <v>37</v>
+      </c>
+      <c r="D26">
+        <v>15</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>5</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>12</v>
+      </c>
+      <c r="S26">
+        <v>2</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>11</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>12</v>
+      </c>
+      <c r="AD26">
+        <v>1</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A28" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28">
+        <v>21</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>2</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>14</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B29" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29">
+        <v>47</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
         <v>6</v>
       </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>6</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="W29">
+        <v>1</v>
+      </c>
+      <c r="X29">
+        <v>6</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>1</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>27</v>
+      </c>
+      <c r="AD29">
         <v>2</v>
       </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>1</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
-      <c r="R26">
-        <v>1</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>1</v>
-      </c>
-      <c r="AC26">
-        <v>5</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>1</v>
-      </c>
-      <c r="AF26">
-        <v>1</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26">
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <v>0</v>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="AE29">
+        <v>6</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>1</v>
+      </c>
+      <c r="AI29">
+        <v>10</v>
+      </c>
+      <c r="AJ29">
+        <v>8</v>
+      </c>
+      <c r="AK29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30">
+        <v>112</v>
+      </c>
+      <c r="D30">
+        <v>84</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>87</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>84</v>
+      </c>
+      <c r="J30">
+        <v>84</v>
+      </c>
+      <c r="K30">
+        <v>84</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>1</v>
+      </c>
+      <c r="S30">
+        <v>1</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>27</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>1</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B31" t="s">
         <v>177</v>
       </c>
-      <c r="C27">
+      <c r="C31">
         <v>81</v>
       </c>
-      <c r="D27">
+      <c r="D31">
         <v>3</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
         <v>2</v>
-      </c>
-      <c r="R27">
-        <v>3</v>
-      </c>
-      <c r="S27">
-        <v>2</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>1</v>
-      </c>
-      <c r="V27">
-        <v>1</v>
-      </c>
-      <c r="W27">
-        <v>1</v>
-      </c>
-      <c r="X27">
-        <v>2</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>4</v>
-      </c>
-      <c r="AB27">
-        <v>1</v>
-      </c>
-      <c r="AC27">
-        <v>72</v>
-      </c>
-      <c r="AD27">
-        <v>1</v>
-      </c>
-      <c r="AE27">
-        <v>2</v>
-      </c>
-      <c r="AF27">
-        <v>1</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27">
-        <v>0</v>
-      </c>
-      <c r="AI27">
-        <v>0</v>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>178</v>
-      </c>
-      <c r="B28" t="s">
-        <v>179</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AI28">
-        <v>0</v>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>180</v>
-      </c>
-      <c r="B29" t="s">
-        <v>181</v>
-      </c>
-      <c r="C29">
-        <v>8</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>3</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>3</v>
-      </c>
-      <c r="R29">
-        <v>7</v>
-      </c>
-      <c r="S29">
-        <v>8</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>7</v>
-      </c>
-      <c r="V29">
-        <v>7</v>
-      </c>
-      <c r="W29">
-        <v>7</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>8</v>
-      </c>
-      <c r="AB29">
-        <v>6</v>
-      </c>
-      <c r="AC29">
-        <v>1</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>8</v>
-      </c>
-      <c r="AF29">
-        <v>6</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29">
-        <v>0</v>
-      </c>
-      <c r="AI29">
-        <v>0</v>
-      </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
-      <c r="AK29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>182</v>
-      </c>
-      <c r="B30" t="s">
-        <v>183</v>
-      </c>
-      <c r="C30">
-        <v>12</v>
-      </c>
-      <c r="D30">
-        <v>10</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>11</v>
-      </c>
-      <c r="S30">
-        <v>7</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-      <c r="AC30">
-        <v>1</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AI30">
-        <v>0</v>
-      </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
-      <c r="AK30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>184</v>
-      </c>
-      <c r="B31" t="s">
-        <v>185</v>
-      </c>
-      <c r="C31">
-        <v>26</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31">
-        <v>3</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
       </c>
       <c r="R31">
         <v>3</v>
       </c>
       <c r="S31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T31">
         <v>0</v>
@@ -9274,7 +9268,7 @@
         <v>1</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y31">
         <v>0</v>
@@ -9283,278 +9277,278 @@
         <v>0</v>
       </c>
       <c r="AA31">
+        <v>4</v>
+      </c>
+      <c r="AB31">
+        <v>1</v>
+      </c>
+      <c r="AC31">
+        <v>72</v>
+      </c>
+      <c r="AD31">
+        <v>1</v>
+      </c>
+      <c r="AE31">
+        <v>2</v>
+      </c>
+      <c r="AF31">
+        <v>1</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32">
+        <v>17</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>17</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33">
+        <v>24</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>7</v>
+      </c>
+      <c r="AB33">
+        <v>1</v>
+      </c>
+      <c r="AC33">
+        <v>14</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>1</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" t="s">
+        <v>181</v>
+      </c>
+      <c r="C34">
+        <v>12</v>
+      </c>
+      <c r="D34">
         <v>10</v>
       </c>
-      <c r="AB31">
-        <v>1</v>
-      </c>
-      <c r="AC31">
-        <v>20</v>
-      </c>
-      <c r="AD31">
-        <v>1</v>
-      </c>
-      <c r="AE31">
-        <v>3</v>
-      </c>
-      <c r="AF31">
-        <v>1</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31">
-        <v>2</v>
-      </c>
-      <c r="AI31">
-        <v>0</v>
-      </c>
-      <c r="AJ31">
-        <v>2</v>
-      </c>
-      <c r="AK31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>186</v>
-      </c>
-      <c r="B32" t="s">
-        <v>187</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>1</v>
-      </c>
-      <c r="AC32">
-        <v>2</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>1</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>1</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>1</v>
-      </c>
-      <c r="AK32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" t="s">
-        <v>189</v>
-      </c>
-      <c r="C33">
-        <v>19</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
-      </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
-      </c>
-      <c r="AB33">
-        <v>0</v>
-      </c>
-      <c r="AC33">
-        <v>19</v>
-      </c>
-      <c r="AD33">
-        <v>0</v>
-      </c>
-      <c r="AE33">
-        <v>0</v>
-      </c>
-      <c r="AF33">
-        <v>0</v>
-      </c>
-      <c r="AG33">
-        <v>0</v>
-      </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
-      <c r="AI33">
-        <v>0</v>
-      </c>
-      <c r="AJ33">
-        <v>0</v>
-      </c>
-      <c r="AK33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>190</v>
-      </c>
-      <c r="B34" t="s">
-        <v>191</v>
-      </c>
-      <c r="C34">
-        <v>25</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
       <c r="E34">
         <v>0</v>
       </c>
@@ -9595,10 +9589,10 @@
         <v>0</v>
       </c>
       <c r="R34">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>0</v>
@@ -9625,10 +9619,10 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AD34">
         <v>0</v>
@@ -9637,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AG34">
         <v>0</v>
@@ -9656,17 +9650,17 @@
       </c>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>192</v>
+      <c r="A35" s="8" t="s">
+        <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="C35">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -9690,7 +9684,7 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -9711,19 +9705,19 @@
         <v>0</v>
       </c>
       <c r="S35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T35">
         <v>0</v>
       </c>
       <c r="U35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35">
         <v>0</v>
@@ -9735,13 +9729,13 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="AD35">
         <v>0</v>
@@ -9750,7 +9744,7 @@
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG35">
         <v>0</v>
@@ -9768,120 +9762,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>194</v>
-      </c>
-      <c r="B36" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36">
-        <v>47</v>
-      </c>
-      <c r="D36">
-        <v>7</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>6</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-      <c r="L36">
-        <v>1</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36">
-        <v>6</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>1</v>
-      </c>
-      <c r="V36">
-        <v>1</v>
-      </c>
-      <c r="W36">
-        <v>1</v>
-      </c>
-      <c r="X36">
-        <v>6</v>
-      </c>
-      <c r="Y36">
-        <v>0</v>
-      </c>
-      <c r="Z36">
-        <v>0</v>
-      </c>
-      <c r="AA36">
-        <v>1</v>
-      </c>
-      <c r="AB36">
-        <v>0</v>
-      </c>
-      <c r="AC36">
-        <v>27</v>
-      </c>
-      <c r="AD36">
-        <v>2</v>
-      </c>
-      <c r="AE36">
-        <v>6</v>
-      </c>
-      <c r="AF36">
-        <v>0</v>
-      </c>
-      <c r="AG36">
-        <v>0</v>
-      </c>
-      <c r="AH36">
-        <v>1</v>
-      </c>
-      <c r="AI36">
-        <v>10</v>
-      </c>
-      <c r="AJ36">
-        <v>8</v>
-      </c>
-      <c r="AK36">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AK35">
+    <sortCondition ref="A1:A35"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
